--- a/APAC-Publication-Calendar-Master-5.xlsx
+++ b/APAC-Publication-Calendar-Master-5.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Lists" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Publications'!$B$2:$P$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Publications'!$B$2:$R$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -104,6 +104,27 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF25273A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF25273A"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -179,7 +200,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -356,6 +377,19 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -367,7 +401,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -440,6 +474,22 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8D7DA"/>
+          <bgColor rgb="FFF8D7DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF3CD"/>
+          <bgColor rgb="FFFFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -688,13 +738,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:B114"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:B137"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" style="30" min="1" max="1"/>
     <col width="110" customWidth="1" style="30" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="27.75" customHeight="1" s="31">
       <c r="B2" s="32" t="inlineStr">
         <is>
@@ -720,9 +771,9 @@
       <c r="B5" s="33" t="n"/>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="31">
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>What changed in this version (v3)</t>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>What changed in this version (v4)</t>
         </is>
       </c>
     </row>
@@ -762,643 +813,784 @@
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="31">
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>• Recurring publications are projected on the LAST calendar day of each month for the next 24 months.</t>
+      <c r="B12" s="62" t="inlineStr">
+        <is>
+          <t>• Recurring publications without an exact date are now projected on an ESTIMATED date derived from a Recurring Timing Window (Early / Mid / Late month), snapped to the LAST BUSINESS DAY of the relevant period. If no window is given, the fallback is the LAST BUSINESS DAY of the month (changed from last calendar day).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="31">
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>• NEW — Start Date: optional per-row date that controls when a recurring series begins. Future instances are generated from the Start Date onward.</t>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>• NEW — Recurring Timing Window: dropdown (Early month / Mid-month / Late month / TBD) that sets the estimated day for recurring rows when no exact date is known.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="7.5" customHeight="1" s="31">
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
+        <is>
+          <t>• NEW — Date Confidence: dropdown (Confirmed / Estimated / TBD). Leave blank to let the platform infer it; an owner-entered value overrides inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" s="31">
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>• Start Date is now REQUIRED for recurring rows (it was optional in v3). If left blank, the series is projected from the upload date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="31">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>• NEW — Lead Author: optional named owner of the publication (separate from the broader Team field).</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="21.75" customHeight="1" s="31">
-      <c r="B15" s="35" t="inlineStr">
+    <row r="17" ht="14.25" customHeight="1" s="31">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>• Publication Name must contain the market/city name (see field 3) so each report is self-identifying on the live calendar.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="31">
-      <c r="B16" s="33" t="n"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1" s="31">
-      <c r="B17" s="36" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="31">
+      <c r="B18" s="33" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="31">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>How to fill in each column</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="31">
-      <c r="B18" s="33" t="inlineStr">
+    <row r="20" ht="7.5" customHeight="1" s="31">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Work left to right. Click any cell to see its inline prompt. Required fields are noted below.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="31">
-      <c r="B19" s="33" t="n"/>
-    </row>
-    <row r="20" ht="7.5" customHeight="1" s="31">
-      <c r="B20" s="37" t="inlineStr">
+    <row r="21" ht="21.75" customHeight="1" s="31">
+      <c r="B21" s="33" t="n"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1" s="31">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>1. Country  (required)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="21.75" customHeight="1" s="31">
-      <c r="B21" s="33" t="inlineStr">
+    <row r="23" ht="19.5" customHeight="1" s="31">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Pick from the dropdown. 'Global' = cross-APAC reports without a regional focus. 'Asia Pacific' = covers the broader APAC region.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1" s="31">
-      <c r="B22" s="33" t="n"/>
-    </row>
-    <row r="23" ht="19.5" customHeight="1" s="31">
-      <c r="B23" s="37" t="inlineStr">
+    <row r="24" ht="19.5" customHeight="1" s="31">
+      <c r="B24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="7.5" customHeight="1" s="31">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>2. City / State  (optional)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1" s="31">
-      <c r="B24" s="33" t="inlineStr">
+    <row r="26" ht="21.75" customHeight="1" s="31">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Free text. Use for sub-market reports (e.g. 'Tokyo', 'Mumbai', 'NSW'). Leave blank for country-wide or regional reports.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" s="31">
-      <c r="B25" s="33" t="n"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" s="31">
-      <c r="B26" s="37" t="inlineStr">
+    <row r="27" ht="19.5" customHeight="1" s="31">
+      <c r="B27" s="33" t="n"/>
+    </row>
+    <row r="28" ht="7.5" customHeight="1" s="31">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>3. Publication Name  (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19.5" customHeight="1" s="31">
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>REQUIRED: include the market or city in the name so the report is self-identifying (e.g. 'Hong Kong', 'Tokyo', 'Australia'). The live calendar shows the name with no separate market label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="7.5" customHeight="1" s="31">
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>Duplicate publication names are flagged in RED on this sheet — rename so each base title is unique.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="31">
       <c r="B29" s="35" t="inlineStr">
         <is>
+          <t>REQUIRED: include the market or city in the name so the report is self-identifying (e.g. 'Hong Kong', 'Tokyo', 'Australia'). The live calendar shows the name with no separate market label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1" s="31">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Duplicate publication names are flagged in RED on this sheet — rename so each base title is unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1" s="31">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
           <t>The base title. For recurring publications, do NOT include the year or period suffix — the platform appends it automatically. Examples:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1" s="31">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Good:  Asia Pacific Investment Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="7.5" customHeight="1" s="31">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Good:  Hong Kong Office Market Watch</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="31">
       <c r="B32" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Good:  Asia Pacific Investment Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="31.5" customHeight="1" s="31">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Good:  Hong Kong Office Market Watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="31.5" customHeight="1" s="31">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Avoid: Asia Pacific Investment Quarterly Q1 2026   (suffix added by platform)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="31.5" customHeight="1" s="31">
-      <c r="B33" s="33" t="n"/>
-    </row>
-    <row r="34" ht="31.5" customHeight="1" s="31">
-      <c r="B34" s="37" t="inlineStr">
+    <row r="35" ht="31.5" customHeight="1" s="31">
+      <c r="B35" s="33" t="n"/>
+    </row>
+    <row r="36" ht="31.5" customHeight="1" s="31">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>4. Asset Class  (optional but recommended)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="31.5" customHeight="1" s="31">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Free text. For multi-asset reports, separate values with a semicolon and a space:</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="31.5" customHeight="1" s="31">
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Office; Logistics; Capital Markets</t>
         </is>
       </c>
     </row>
     <row r="37" ht="31.5" customHeight="1" s="31">
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>Valid tokens (use these spellings): All, Office, Retail, Logistics, Industrial, Residential, Hospitality, Data Centres, Capital Markets, Living, Mixed Use.</t>
+          <t>Free text. For multi-asset reports, separate values with a semicolon and a space:</t>
         </is>
       </c>
     </row>
     <row r="38" ht="7.5" customHeight="1" s="31">
       <c r="B38" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Office; Logistics; Capital Markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21.75" customHeight="1" s="31">
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Valid tokens (use these spellings): All, Office, Retail, Logistics, Industrial, Residential, Hospitality, Data Centres, Capital Markets, Living, Mixed Use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="31.5" customHeight="1" s="31">
+      <c r="B40" s="33" t="inlineStr">
+        <is>
           <t>Use 'All' for cross-asset reports.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="21.75" customHeight="1" s="31">
-      <c r="B39" s="33" t="n"/>
-    </row>
-    <row r="40" ht="31.5" customHeight="1" s="31">
-      <c r="B40" s="37" t="inlineStr">
+    <row r="41" ht="31.5" customHeight="1" s="31">
+      <c r="B41" s="33" t="n"/>
+    </row>
+    <row r="42" ht="31.5" customHeight="1" s="31">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>5. Publication Type  (required)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="31.5" customHeight="1" s="31">
-      <c r="B41" s="33" t="inlineStr">
+    <row r="43" ht="31.5" customHeight="1" s="31">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>Pick one from the dropdown. Options: Market Reports, Newsletter, Quarterly Outlooks, Sector Updates, Thought Leadership, White Papers, Blogs.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="31.5" customHeight="1" s="31">
-      <c r="B42" s="33" t="n"/>
-    </row>
-    <row r="43" ht="31.5" customHeight="1" s="31">
-      <c r="B43" s="37" t="inlineStr">
+    <row r="44" ht="14.25" customHeight="1" s="31">
+      <c r="B44" s="33" t="n"/>
+    </row>
+    <row r="45" ht="7.5" customHeight="1" s="31">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>6. Language  (required)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1" s="31">
-      <c r="B44" s="33" t="inlineStr">
+    <row r="46" ht="14.25" customHeight="1" s="31">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>'English' as default. Multi-language reports may use a semicolon separator — e.g. 'English; Chinese (Traditional)'.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" s="31">
-      <c r="B45" s="33" t="n"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1" s="31">
-      <c r="B46" s="37" t="inlineStr">
+    <row r="47" ht="14.25" customHeight="1" s="31">
+      <c r="B47" s="33" t="n"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" s="31">
+      <c r="B48" s="37" t="inlineStr">
         <is>
           <t>7. Frequency  (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1" s="31">
-      <c r="B47" s="33" t="inlineStr">
-        <is>
-          <t>Pick one:</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="31">
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Annually    — once a year</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="31">
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Biannually  — twice a year</t>
+          <t>Pick one:</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="31">
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Quarterly   — four times a year</t>
+          <t xml:space="preserve">    Annually    — once a year</t>
         </is>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" s="31">
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Monthly     — twelve times a year</t>
+          <t xml:space="preserve">    Biannually  — twice a year</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="31">
       <c r="B52" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Quarterly   — four times a year</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="7.5" customHeight="1" s="31">
+      <c r="B53" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Monthly     — twelve times a year</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" s="31">
+      <c r="B54" s="33" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Ad Hoc      — one-off; not part of a recurring series</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" s="31">
-      <c r="B53" s="33" t="n"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1" s="31">
-      <c r="B54" s="37" t="inlineStr">
+    <row r="55" ht="14.25" customHeight="1" s="31">
+      <c r="B55" s="33" t="n"/>
+    </row>
+    <row r="56" ht="14.25" customHeight="1" s="31">
+      <c r="B56" s="37" t="inlineStr">
         <is>
           <t>8. Recurring Months  (required if Frequency ≠ Ad Hoc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1" s="31">
-      <c r="B55" s="33" t="inlineStr">
-        <is>
-          <t>Tells the platform which months the publication drops each year. Format rules:</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1" s="31">
-      <c r="B56" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Use 3-letter month tokens, exact spelling:  Jan Feb Mar Apr May Jun Jul Aug Sep Oct Nov Dec</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="31">
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Separate multiple months with a semicolon. A space after the semicolon is optional.</t>
+          <t>Tells the platform which months the publication drops each year. Format rules:</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="31">
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Order doesn't matter — the platform sorts chronologically.</t>
+          <t xml:space="preserve">  • Use 3-letter month tokens, exact spelling:  Jan Feb Mar Apr May Jun Jul Aug Sep Oct Nov Dec</t>
         </is>
       </c>
     </row>
     <row r="59" ht="7.5" customHeight="1" s="31">
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Case-insensitive (mar / MAR / Mar all work), but stick to title case for readability.</t>
+          <t xml:space="preserve">  • Separate multiple months with a semicolon. A space after the semicolon is optional.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="31">
-      <c r="B60" s="33" t="n"/>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Order doesn't matter — the platform sorts chronologically.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="31">
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>Number of months must match Frequency:</t>
+          <t xml:space="preserve">  • Case-insensitive (mar / MAR / Mar all work), but stick to title case for readability.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1" s="31">
-      <c r="B62" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Annually    → 1 month     e.g.  Nov</t>
-        </is>
-      </c>
+      <c r="B62" s="33" t="n"/>
     </row>
     <row r="63" ht="28.5" customHeight="1" s="31">
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Biannually  → 2 months    e.g.  Jun; Dec</t>
+          <t>Number of months must match Frequency:</t>
         </is>
       </c>
     </row>
     <row r="64" ht="7.5" customHeight="1" s="31">
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Quarterly   → 4 months    e.g.  Mar; Jun; Sep; Dec</t>
+          <t xml:space="preserve">    Annually    → 1 month     e.g.  Nov</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21.75" customHeight="1" s="31">
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Monthly     → leave blank (all 12 months auto-applied)</t>
+          <t xml:space="preserve">    Biannually  → 2 months    e.g.  Jun; Dec</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="31">
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ad Hoc      → leave blank</t>
+          <t xml:space="preserve">    Quarterly   → 4 months    e.g.  Mar; Jun; Sep; Dec</t>
         </is>
       </c>
     </row>
     <row r="67" ht="7.5" customHeight="1" s="31">
-      <c r="B67" s="33" t="n"/>
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Monthly     → leave blank (all 12 months auto-applied)</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="21.75" customHeight="1" s="31">
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>Common rejection reasons (the upload report will flag these):</t>
+          <t xml:space="preserve">    Ad Hoc      → leave blank</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1" s="31">
-      <c r="B69" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    'March; June'       — use 3-letter tokens (Mar; Jun)</t>
-        </is>
-      </c>
+      <c r="B69" s="33" t="n"/>
     </row>
     <row r="70" ht="7.5" customHeight="1" s="31">
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Mar, Jun, Sep, Dec' — use semicolons, not commas</t>
+          <t>Common rejection reasons (the upload report will flag these):</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21.75" customHeight="1" s="31">
       <c r="B71" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Mar/Jun/Sep/Dec'   — use semicolons, not slashes</t>
+          <t xml:space="preserve">    'March; June'       — use 3-letter tokens (Mar; Jun)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1" s="31">
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    'Mrch; Jun'         — typo in month token</t>
+          <t xml:space="preserve">    'Mar, Jun, Sep, Dec' — use semicolons, not commas</t>
         </is>
       </c>
     </row>
     <row r="73" ht="7.5" customHeight="1" s="31">
       <c r="B73" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">    'Mar/Jun/Sep/Dec'   — use semicolons, not slashes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="21.75" customHeight="1" s="31">
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'Mrch; Jun'         — typo in month token</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="14.25" customHeight="1" s="31">
+      <c r="B75" s="33" t="inlineStr">
+        <is>
           <t xml:space="preserve">    'Mar; Jun; Sep'     — only 3 months on a Quarterly row</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="21.75" customHeight="1" s="31">
-      <c r="B74" s="33" t="n"/>
-    </row>
-    <row r="75" ht="14.25" customHeight="1" s="31">
-      <c r="B75" s="37" t="inlineStr">
+    <row r="76" ht="7.5" customHeight="1" s="31">
+      <c r="B76" s="33" t="n"/>
+    </row>
+    <row r="77" ht="21.75" customHeight="1" s="31">
+      <c r="B77" s="37" t="inlineStr">
         <is>
           <t>9. Expected Publication Date  (required for Ad Hoc; leave BLANK for recurring)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="7.5" customHeight="1" s="31">
-      <c r="B76" s="33" t="inlineStr">
-        <is>
-          <t>Format: YYYY-MM-DD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="21.75" customHeight="1" s="31">
-      <c r="B77" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Ad Hoc rows: enter the planned date. This is what the calendar pins it to.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1" s="31">
       <c r="B78" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Recurring rows: leave blank. The platform auto-generates one instance per Recurring Month on the LAST calendar day of that month, projected forward 24 months.</t>
+          <t>Format: YYYY-MM-DD.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1" s="31">
       <c r="B79" s="33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • Ad Hoc rows: enter the planned date. This is what the calendar pins it to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14.25" customHeight="1" s="31">
+      <c r="B80" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Recurring rows: usually leave blank — the platform estimates the date from the Recurring Timing Window (see field 11). If you DO enter a date here on a recurring row, it is used ONLY for the next upcoming occurrence (an exact override); all later instances revert to the estimated timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="14.25" customHeight="1" s="31">
+      <c r="B81" s="33" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • If the date is not yet known, leave blank — the row appears in the TBD panel on the live site.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="14.25" customHeight="1" s="31">
-      <c r="B80" s="38" t="inlineStr">
-        <is>
-          <t>10. Start Date  (optional; recurring rows only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1" s="31">
-      <c r="B81" s="35" t="inlineStr">
-        <is>
-          <t>Format: YYYY-MM-DD. Sets when a recurring series BEGINS — the platform only generates instances on/after this date.</t>
-        </is>
-      </c>
-    </row>
     <row r="82" ht="14.25" customHeight="1" s="31">
-      <c r="B82" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Leave blank to start projecting from the upload date (current behaviour).</t>
+      <c r="B82" s="63" t="inlineStr">
+        <is>
+          <t>10. Start Date  (REQUIRED for recurring rows; leave blank for Ad Hoc)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1" s="31">
-      <c r="B83" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Use it to launch a new recurring report in a future month, or to backfill from an earlier start.</t>
+      <c r="B83" s="62" t="inlineStr">
+        <is>
+          <t>Format: YYYY-MM-DD. Sets when a recurring series BEGINS — the platform only generates instances on/after this date. Start Date is backend-only and is NOT shown in the detail panel on the live site.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1" s="31">
-      <c r="B84" s="33" t="n"/>
+      <c r="B84" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • REQUIRED for recurring rows. If left blank, the series is projected from the upload date.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="14.25" customHeight="1" s="31">
-      <c r="B85" s="34" t="inlineStr">
-        <is>
-          <t>11. Team  (optional)</t>
+      <c r="B85" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • If the Start Date falls mid-month, that month is still used if the estimated day still fits the chosen timing window.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1" s="31">
-      <c r="B86" s="35" t="inlineStr">
+      <c r="B86" s="63" t="inlineStr">
+        <is>
+          <t>11. Recurring Timing Window  (dropdown; recurring rows only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="7.5" customHeight="1" s="31">
+      <c r="B87" s="62" t="inlineStr">
+        <is>
+          <t>Dropdown ONLY (no free text). Sets the estimated day-of-month for recurring rows when no exact date is known. Allowed values:</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="21.75" customHeight="1" s="31">
+      <c r="B88" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Early month  → estimated on the 5th  (snapped to the last business day on/before the 5th, same month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28.5" customHeight="1" s="31">
+      <c r="B89" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mid-month    → estimated on the 15th (snapped to a business day, same month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="14.25" customHeight="1" s="31">
+      <c r="B90" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Late month   → estimated on the 25th (snapped to a business day, same month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="14.25" customHeight="1" s="31">
+      <c r="B91" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TBD          → no estimate; the fallback (last business day of the month) is used and the row still appears on the calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14.25" customHeight="1" s="31"/>
+    <row r="93" ht="14.25" customHeight="1" s="31">
+      <c r="B93" s="63" t="inlineStr">
+        <is>
+          <t>12. Date Confidence  (dropdown; optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1" s="31">
+      <c r="B94" s="62" t="inlineStr">
+        <is>
+          <t>Dropdown (Confirmed / Estimated / TBD). Optional — leave blank to let the platform infer it. An owner-entered value always overrides the inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1" s="31">
+      <c r="B95" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Confirmed → the instance has an exact, known date (e.g. an Expected Publication Date / next-occurrence override).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1" s="31">
+      <c r="B96" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Estimated → the date comes from a Recurring Timing Window (or the last-business-day fallback).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="14.25" customHeight="1" s="31">
+      <c r="B97" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TBD       → no date and no timing window yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14.25" customHeight="1" s="31">
+      <c r="B98" s="33" t="n"/>
+    </row>
+    <row r="99" ht="14.25" customHeight="1" s="31">
+      <c r="B99" s="34" t="inlineStr">
+        <is>
+          <t>13. Team  (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="14.25" customHeight="1" s="31">
+      <c r="B100" s="35" t="inlineStr">
         <is>
           <t>Free text. The team, desk, or group responsible (e.g. 'APAC Research', 'Australia Research'). For a specific person, use Lead Author.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="7.5" customHeight="1" s="31">
-      <c r="B87" s="38" t="inlineStr">
-        <is>
-          <t>12. Lead Author  (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="21.75" customHeight="1" s="31">
-      <c r="B88" s="35" t="inlineStr">
+    <row r="101" ht="15" customHeight="1" s="31">
+      <c r="B101" s="38" t="inlineStr">
+        <is>
+          <t>14. Lead Author  (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="27.75" customHeight="1" s="31">
+      <c r="B102" s="35" t="inlineStr">
         <is>
           <t>Free text. The named individual who owns/authors the publication (e.g. 'Simon Smith'). Distinct from Team, which can be a group.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="28.5" customHeight="1" s="31"/>
-    <row r="90" ht="14.25" customHeight="1" s="31">
-      <c r="B90" s="33" t="n"/>
-    </row>
-    <row r="91" ht="14.25" customHeight="1" s="31">
-      <c r="B91" s="34" t="inlineStr">
-        <is>
-          <t>13. Notes  (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1" s="31">
-      <c r="B92" s="33" t="inlineStr">
-        <is>
-          <t>Free text. Internal context, key arguments, or themes. Shown in the detail panel on the live site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1" s="31">
-      <c r="B93" s="33" t="n"/>
-    </row>
-    <row r="94" ht="14.25" customHeight="1" s="31">
-      <c r="B94" s="34" t="inlineStr">
-        <is>
-          <t>14. Report Scope  (required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1" s="31">
-      <c r="B95" s="33" t="inlineStr">
-        <is>
-          <t>Regional = covers multiple APAC markets (colour-coded Savills Yellow on the live site).</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="14.25" customHeight="1" s="31">
-      <c r="B96" s="33" t="inlineStr">
-        <is>
-          <t>In-Country = focused on one market (colour-coded Savills Steel Grey on the live site).</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1" s="31">
-      <c r="B97" s="33" t="n"/>
-    </row>
-    <row r="98" ht="14.25" customHeight="1" s="31">
-      <c r="B98" s="34" t="inlineStr">
-        <is>
-          <t>15. Status (future)  (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="14.25" customHeight="1" s="31">
-      <c r="B99" s="33" t="inlineStr">
-        <is>
-          <t>Workflow stage. Stored in the JSON but not displayed in v1 — the leadership view will use it later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="14.25" customHeight="1" s="31">
-      <c r="B100" s="33" t="n"/>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="31">
-      <c r="B101" s="36" t="inlineStr">
-        <is>
-          <t>How recurring publications are expanded</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="27.75" customHeight="1" s="31">
-      <c r="B102" s="33" t="inlineStr">
-        <is>
-          <t>When the platform reads a row with Frequency = Annually / Biannually / Quarterly / Monthly:</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="14.25" customHeight="1" s="31">
-      <c r="B103" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Parses Recurring Months into a list (e.g. Mar; Jun; Sep; Dec → [3, 6, 9, 12]). Monthly uses all 12 automatically.</t>
-        </is>
-      </c>
-    </row>
+    <row r="103" ht="14.25" customHeight="1" s="31"/>
     <row r="104" ht="14.25" customHeight="1" s="31">
-      <c r="B104" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Generates one instance per chosen month, on the LAST calendar day of the month.</t>
-        </is>
-      </c>
+      <c r="B104" s="33" t="n"/>
     </row>
     <row r="105" ht="14.25" customHeight="1" s="31">
-      <c r="B105" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Projects forward 24 months from the upload date.</t>
+      <c r="B105" s="34" t="inlineStr">
+        <is>
+          <t>15. Notes  (optional)</t>
         </is>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1" s="31">
       <c r="B106" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Auto-appends a period suffix to the title:</t>
+          <t>Free text. Internal context, key arguments, or themes. Shown in the detail panel on the live site.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1" s="31">
-      <c r="B107" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Annually    → year only            'Asia Pacific Outlook — 2026'</t>
-        </is>
-      </c>
+      <c r="B107" s="33" t="n"/>
     </row>
     <row r="108" ht="14.25" customHeight="1" s="31">
-      <c r="B108" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Biannually  → half-year notation   'APAC Logistics — H1 2026'</t>
+      <c r="B108" s="34" t="inlineStr">
+        <is>
+          <t>16. Report Scope  (required)</t>
         </is>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1" s="31">
       <c r="B109" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Quarterly   → quarter notation     'APAC Investment Quarterly — Q1 2026'</t>
+          <t>Regional = covers multiple APAC markets (colour-coded Savills Yellow on the live site).</t>
         </is>
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1" s="31">
       <c r="B110" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Monthly     → month + year         'Newsletter — Mar 2026'</t>
+          <t>In-Country = focused on one market (colour-coded Savills Steel Grey on the live site).</t>
         </is>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1" s="31">
-      <c r="B111" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Tags each instance with a ↻ icon and a dashed border on the live calendar.</t>
-        </is>
-      </c>
+      <c r="B111" s="33" t="n"/>
     </row>
     <row r="112" ht="14.25" customHeight="1" s="31">
-      <c r="B112" s="33" t="n"/>
+      <c r="B112" s="34" t="inlineStr">
+        <is>
+          <t>17. Status (future)  (optional)</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="31">
-      <c r="B113" s="36" t="inlineStr">
+      <c r="B113" s="33" t="inlineStr">
+        <is>
+          <t>Workflow stage. Stored in the JSON but not displayed in v1 — the leadership view will use it later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="27.75" customHeight="1" s="31">
+      <c r="B114" s="33" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="36" t="inlineStr">
+        <is>
+          <t>How recurring publications are expanded</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="62" t="inlineStr">
+        <is>
+          <t>When the platform reads a row with Frequency = Annually / Biannually / Quarterly / Monthly:</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Parses Recurring Months into a list (e.g. Mar; Jun; Sep; Dec → [3, 6, 9, 12]). Monthly uses all 12 automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Determines the day-of-month for each instance, in priority order:</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       a. Exact next-occurrence override — if an Expected Publication Date is set, it is used for the NEXT upcoming occurrence only (Date Confidence = Confirmed for that instance); later instances revert to the estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       b. Recurring Timing Window — Early month → 5th, Mid-month → 15th, Late month → 25th, each snapped to a business day (weekends move to the previous business day, staying in the same month). Date Confidence = Estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       c. Fallback — if no timing window is given (or TBD), the instance lands on the LAST BUSINESS DAY of the month (weekends/Mon–Fri only; public holidays are ignored for this calculation). Date Confidence = Estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Generates instances on/after the Start Date, projected forward 24 months from the upload date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Infers Date Confidence when the owner leaves it blank: exact date → Confirmed; timing window or fallback → Estimated; no date and no window → TBD. An owner-entered Date Confidence always overrides this inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. Auto-appends a period suffix to the title (Annually → year; Biannually → H1/H2; Quarterly → Q1–Q4; Monthly → month + year).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Tags each instance with a ↻ icon and a dashed border on the live calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="33" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="64" t="inlineStr">
+        <is>
+          <t>Inconsistency flags on this sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="62" t="inlineStr">
+        <is>
+          <t>Cells are highlighted when the row's date settings contradict each other. Fix the highlighted cell, then re-upload:</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • RED on Date Confidence — marked Confirmed but no Expected Publication Date is set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • RED on Start Date — a recurring row (Annually / Biannually / Quarterly / Monthly) with no Start Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • RED on Date Confidence — Estimated on a non-recurring row with no timing window (nothing to estimate from).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • AMBER on Recurring Timing Window — a timing window set on an Ad Hoc row (windows apply to recurring rows only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • AMBER on TBD cells — a reminder that the value is still a placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="36" t="inlineStr">
         <is>
           <t>Filtering tip</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="27.75" customHeight="1" s="31">
-      <c r="B114" s="33" t="inlineStr">
+    <row r="137">
+      <c r="B137" s="33" t="inlineStr">
         <is>
           <t>Row 2 has auto-filter on every column. Click the dropdown arrow in any header to filter by Country, Frequency, Publication Type, etc. Recurring Months filters via 'contains' (search 'Mar' to see all Q1 publications).</t>
         </is>
@@ -1417,8 +1609,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B1:Q81"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B1:S81"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" style="30" min="1" max="1"/>
     <col width="16" customWidth="1" style="30" min="2" max="2"/>
@@ -1431,10 +1623,13 @@
     <col width="28" customWidth="1" style="30" min="9" max="9"/>
     <col width="18" customWidth="1" style="30" min="10" max="10"/>
     <col width="14" customWidth="1" style="30" min="11" max="11"/>
-    <col width="40" customWidth="1" style="30" min="12" max="12"/>
-    <col width="18" customWidth="1" style="30" min="13" max="13"/>
-    <col width="14" customWidth="1" style="30" min="14" max="14"/>
-    <col width="10" customWidth="1" style="30" min="15" max="15"/>
+    <col width="22" customWidth="1" style="30" min="12" max="12"/>
+    <col width="16" customWidth="1" style="30" min="13" max="13"/>
+    <col width="18" customWidth="1" style="30" min="14" max="14"/>
+    <col width="20" customWidth="1" style="30" min="15" max="15"/>
+    <col width="40" customWidth="1" style="31" min="16" max="16"/>
+    <col width="14" customWidth="1" style="31" min="17" max="17"/>
+    <col width="16" customWidth="1" style="31" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" s="31">
@@ -1497,30 +1692,40 @@
       </c>
       <c r="L2" s="40" t="inlineStr">
         <is>
+          <t>Recurring Timing Window</t>
+        </is>
+      </c>
+      <c r="M2" s="40" t="inlineStr">
+        <is>
+          <t>Date Confidence</t>
+        </is>
+      </c>
+      <c r="N2" s="40" t="inlineStr">
+        <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="M2" s="40" t="inlineStr">
+      <c r="O2" s="40" t="inlineStr">
         <is>
           <t>Lead Author</t>
         </is>
       </c>
-      <c r="N2" s="40" t="inlineStr">
+      <c r="P2" s="40" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O2" s="40" t="inlineStr">
+      <c r="Q2" s="40" t="inlineStr">
         <is>
           <t>Report Scope</t>
         </is>
       </c>
-      <c r="P2" s="40" t="inlineStr">
+      <c r="R2" s="40" t="inlineStr">
         <is>
           <t>Status (future)</t>
         </is>
       </c>
-      <c r="Q2" s="41" t="n"/>
+      <c r="S2" s="41" t="n"/>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="31">
       <c r="B3" s="42" t="inlineStr">
@@ -1565,19 +1770,21 @@
       </c>
       <c r="J3" s="45" t="n"/>
       <c r="K3" s="46" t="n"/>
-      <c r="L3" s="47" t="inlineStr">
+      <c r="L3" s="42" t="n"/>
+      <c r="M3" s="42" t="n"/>
+      <c r="N3" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M3" s="48" t="n"/>
-      <c r="O3" s="42" t="inlineStr">
+      <c r="O3" s="48" t="n"/>
+      <c r="Q3" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P3" s="42" t="n"/>
-      <c r="Q3" s="49" t="n"/>
+      <c r="R3" s="42" t="n"/>
+      <c r="S3" s="49" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="31">
       <c r="B4" s="42" t="inlineStr">
@@ -1621,19 +1828,21 @@
         </is>
       </c>
       <c r="K4" s="46" t="n"/>
-      <c r="L4" s="47" t="inlineStr">
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+      <c r="N4" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M4" s="48" t="n"/>
-      <c r="O4" s="42" t="inlineStr">
+      <c r="O4" s="48" t="n"/>
+      <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P4" s="42" t="n"/>
-      <c r="Q4" s="49" t="n"/>
+      <c r="R4" s="42" t="n"/>
+      <c r="S4" s="49" t="n"/>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="31">
       <c r="B5" s="42" t="inlineStr">
@@ -1678,19 +1887,21 @@
       </c>
       <c r="J5" s="45" t="n"/>
       <c r="K5" s="46" t="n"/>
-      <c r="L5" s="47" t="inlineStr">
+      <c r="L5" s="42" t="n"/>
+      <c r="M5" s="42" t="n"/>
+      <c r="N5" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M5" s="48" t="n"/>
-      <c r="O5" s="42" t="inlineStr">
+      <c r="O5" s="48" t="n"/>
+      <c r="Q5" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P5" s="42" t="n"/>
-      <c r="Q5" s="49" t="n"/>
+      <c r="R5" s="42" t="n"/>
+      <c r="S5" s="49" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="31">
       <c r="B6" s="42" t="inlineStr">
@@ -1735,19 +1946,21 @@
       </c>
       <c r="J6" s="45" t="n"/>
       <c r="K6" s="46" t="n"/>
-      <c r="L6" s="47" t="inlineStr">
+      <c r="L6" s="42" t="n"/>
+      <c r="M6" s="42" t="n"/>
+      <c r="N6" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M6" s="48" t="n"/>
-      <c r="O6" s="42" t="inlineStr">
+      <c r="O6" s="48" t="n"/>
+      <c r="Q6" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P6" s="42" t="n"/>
-      <c r="Q6" s="49" t="n"/>
+      <c r="R6" s="42" t="n"/>
+      <c r="S6" s="49" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="31">
       <c r="B7" s="42" t="inlineStr">
@@ -1791,19 +2004,21 @@
         </is>
       </c>
       <c r="K7" s="46" t="n"/>
-      <c r="L7" s="47" t="inlineStr">
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M7" s="48" t="n"/>
-      <c r="O7" s="42" t="inlineStr">
+      <c r="O7" s="48" t="n"/>
+      <c r="Q7" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P7" s="42" t="n"/>
-      <c r="Q7" s="49" t="n"/>
+      <c r="R7" s="42" t="n"/>
+      <c r="S7" s="49" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="31">
       <c r="B8" s="42" t="inlineStr">
@@ -1848,19 +2063,21 @@
       </c>
       <c r="J8" s="52" t="n"/>
       <c r="K8" s="46" t="n"/>
-      <c r="L8" s="47" t="inlineStr">
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
+      <c r="N8" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M8" s="48" t="n"/>
-      <c r="O8" s="42" t="inlineStr">
+      <c r="O8" s="48" t="n"/>
+      <c r="Q8" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P8" s="42" t="n"/>
-      <c r="Q8" s="49" t="n"/>
+      <c r="R8" s="42" t="n"/>
+      <c r="S8" s="49" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="31">
       <c r="B9" s="42" t="inlineStr">
@@ -1902,19 +2119,21 @@
         <v>46032</v>
       </c>
       <c r="K9" s="46" t="n"/>
-      <c r="L9" s="47" t="inlineStr">
+      <c r="L9" s="42" t="n"/>
+      <c r="M9" s="42" t="n"/>
+      <c r="N9" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M9" s="48" t="n"/>
-      <c r="O9" s="42" t="inlineStr">
+      <c r="O9" s="48" t="n"/>
+      <c r="Q9" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P9" s="42" t="n"/>
-      <c r="Q9" s="49" t="n"/>
+      <c r="R9" s="42" t="n"/>
+      <c r="S9" s="49" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="31">
       <c r="B10" s="42" t="inlineStr">
@@ -1958,19 +2177,21 @@
         </is>
       </c>
       <c r="K10" s="46" t="n"/>
-      <c r="L10" s="47" t="inlineStr">
+      <c r="L10" s="42" t="n"/>
+      <c r="M10" s="42" t="n"/>
+      <c r="N10" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M10" s="48" t="n"/>
-      <c r="O10" s="42" t="inlineStr">
+      <c r="O10" s="48" t="n"/>
+      <c r="Q10" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P10" s="42" t="n"/>
-      <c r="Q10" s="49" t="n"/>
+      <c r="R10" s="42" t="n"/>
+      <c r="S10" s="49" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="31">
       <c r="B11" s="42" t="inlineStr">
@@ -2014,19 +2235,21 @@
         </is>
       </c>
       <c r="K11" s="46" t="n"/>
-      <c r="L11" s="47" t="inlineStr">
+      <c r="L11" s="42" t="n"/>
+      <c r="M11" s="42" t="n"/>
+      <c r="N11" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M11" s="48" t="n"/>
-      <c r="O11" s="42" t="inlineStr">
+      <c r="O11" s="48" t="n"/>
+      <c r="Q11" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P11" s="42" t="n"/>
-      <c r="Q11" s="49" t="n"/>
+      <c r="R11" s="42" t="n"/>
+      <c r="S11" s="49" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="31">
       <c r="B12" s="42" t="inlineStr">
@@ -2070,19 +2293,21 @@
         </is>
       </c>
       <c r="K12" s="46" t="n"/>
-      <c r="L12" s="47" t="inlineStr">
+      <c r="L12" s="42" t="n"/>
+      <c r="M12" s="42" t="n"/>
+      <c r="N12" s="47" t="inlineStr">
         <is>
           <t>Australia Research</t>
         </is>
       </c>
-      <c r="M12" s="48" t="n"/>
-      <c r="O12" s="42" t="inlineStr">
+      <c r="O12" s="48" t="n"/>
+      <c r="Q12" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P12" s="42" t="n"/>
-      <c r="Q12" s="49" t="n"/>
+      <c r="R12" s="42" t="n"/>
+      <c r="S12" s="49" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="31">
       <c r="B13" s="42" t="inlineStr">
@@ -2127,19 +2352,21 @@
       </c>
       <c r="J13" s="45" t="n"/>
       <c r="K13" s="46" t="n"/>
-      <c r="L13" s="53" t="inlineStr">
+      <c r="L13" s="42" t="n"/>
+      <c r="M13" s="42" t="n"/>
+      <c r="N13" s="53" t="inlineStr">
         <is>
           <t>Indonesia Research</t>
         </is>
       </c>
-      <c r="M13" s="48" t="n"/>
-      <c r="O13" s="42" t="inlineStr">
+      <c r="O13" s="48" t="n"/>
+      <c r="Q13" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P13" s="42" t="n"/>
-      <c r="Q13" s="49" t="n"/>
+      <c r="R13" s="42" t="n"/>
+      <c r="S13" s="49" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="31">
       <c r="B14" s="42" t="inlineStr">
@@ -2184,19 +2411,21 @@
       </c>
       <c r="J14" s="45" t="n"/>
       <c r="K14" s="46" t="n"/>
-      <c r="L14" s="53" t="inlineStr">
+      <c r="L14" s="42" t="n"/>
+      <c r="M14" s="42" t="n"/>
+      <c r="N14" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M14" s="48" t="n"/>
-      <c r="O14" s="42" t="inlineStr">
+      <c r="O14" s="48" t="n"/>
+      <c r="Q14" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P14" s="42" t="n"/>
-      <c r="Q14" s="49" t="n"/>
+      <c r="R14" s="42" t="n"/>
+      <c r="S14" s="49" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="31">
       <c r="B15" s="42" t="inlineStr">
@@ -2241,19 +2470,21 @@
       </c>
       <c r="J15" s="45" t="n"/>
       <c r="K15" s="46" t="n"/>
-      <c r="L15" s="53" t="inlineStr">
+      <c r="L15" s="42" t="n"/>
+      <c r="M15" s="42" t="n"/>
+      <c r="N15" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M15" s="48" t="n"/>
-      <c r="O15" s="42" t="inlineStr">
+      <c r="O15" s="48" t="n"/>
+      <c r="Q15" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P15" s="42" t="n"/>
-      <c r="Q15" s="49" t="n"/>
+      <c r="R15" s="42" t="n"/>
+      <c r="S15" s="49" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="31">
       <c r="B16" s="42" t="inlineStr">
@@ -2298,19 +2529,21 @@
       </c>
       <c r="J16" s="45" t="n"/>
       <c r="K16" s="46" t="n"/>
-      <c r="L16" s="53" t="inlineStr">
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="42" t="n"/>
+      <c r="N16" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M16" s="48" t="n"/>
-      <c r="O16" s="42" t="inlineStr">
+      <c r="O16" s="48" t="n"/>
+      <c r="Q16" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P16" s="42" t="n"/>
-      <c r="Q16" s="49" t="n"/>
+      <c r="R16" s="42" t="n"/>
+      <c r="S16" s="49" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="31">
       <c r="B17" s="42" t="inlineStr">
@@ -2355,20 +2588,22 @@
       </c>
       <c r="J17" s="52" t="n"/>
       <c r="K17" s="46" t="n"/>
-      <c r="L17" s="53" t="inlineStr">
+      <c r="L17" s="42" t="n"/>
+      <c r="M17" s="42" t="n"/>
+      <c r="N17" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M17" s="48" t="n"/>
-      <c r="N17" s="42" t="n"/>
-      <c r="O17" s="42" t="inlineStr">
+      <c r="O17" s="48" t="n"/>
+      <c r="P17" s="42" t="n"/>
+      <c r="Q17" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P17" s="42" t="n"/>
-      <c r="Q17" s="49" t="n"/>
+      <c r="R17" s="42" t="n"/>
+      <c r="S17" s="49" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="31">
       <c r="B18" s="42" t="inlineStr">
@@ -2413,20 +2648,22 @@
       </c>
       <c r="J18" s="52" t="n"/>
       <c r="K18" s="46" t="n"/>
-      <c r="L18" s="53" t="inlineStr">
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="42" t="n"/>
+      <c r="N18" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M18" s="48" t="n"/>
-      <c r="N18" s="42" t="n"/>
-      <c r="O18" s="42" t="inlineStr">
+      <c r="O18" s="48" t="n"/>
+      <c r="P18" s="42" t="n"/>
+      <c r="Q18" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P18" s="42" t="n"/>
-      <c r="Q18" s="49" t="n"/>
+      <c r="R18" s="42" t="n"/>
+      <c r="S18" s="49" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="31">
       <c r="B19" s="42" t="inlineStr">
@@ -2471,20 +2708,22 @@
       </c>
       <c r="J19" s="52" t="n"/>
       <c r="K19" s="46" t="n"/>
-      <c r="L19" s="53" t="inlineStr">
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="42" t="n"/>
+      <c r="N19" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M19" s="48" t="n"/>
-      <c r="N19" s="42" t="n"/>
-      <c r="O19" s="42" t="inlineStr">
+      <c r="O19" s="48" t="n"/>
+      <c r="P19" s="42" t="n"/>
+      <c r="Q19" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P19" s="42" t="n"/>
-      <c r="Q19" s="49" t="n"/>
+      <c r="R19" s="42" t="n"/>
+      <c r="S19" s="49" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="31">
       <c r="B20" s="42" t="inlineStr">
@@ -2529,20 +2768,22 @@
       </c>
       <c r="J20" s="52" t="n"/>
       <c r="K20" s="46" t="n"/>
-      <c r="L20" s="53" t="inlineStr">
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="42" t="n"/>
+      <c r="N20" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M20" s="48" t="n"/>
-      <c r="N20" s="42" t="n"/>
-      <c r="O20" s="42" t="inlineStr">
+      <c r="O20" s="48" t="n"/>
+      <c r="P20" s="42" t="n"/>
+      <c r="Q20" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P20" s="42" t="n"/>
-      <c r="Q20" s="49" t="n"/>
+      <c r="R20" s="42" t="n"/>
+      <c r="S20" s="49" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="31">
       <c r="B21" s="42" t="inlineStr">
@@ -2587,20 +2828,22 @@
       </c>
       <c r="J21" s="52" t="n"/>
       <c r="K21" s="46" t="n"/>
-      <c r="L21" s="53" t="inlineStr">
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="42" t="n"/>
+      <c r="N21" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M21" s="48" t="n"/>
-      <c r="N21" s="42" t="n"/>
-      <c r="O21" s="42" t="inlineStr">
+      <c r="O21" s="48" t="n"/>
+      <c r="P21" s="42" t="n"/>
+      <c r="Q21" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P21" s="42" t="n"/>
-      <c r="Q21" s="49" t="n"/>
+      <c r="R21" s="42" t="n"/>
+      <c r="S21" s="49" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="31">
       <c r="B22" s="42" t="inlineStr">
@@ -2645,20 +2888,22 @@
         </is>
       </c>
       <c r="K22" s="46" t="n"/>
-      <c r="L22" s="53" t="inlineStr">
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="42" t="n"/>
+      <c r="N22" s="53" t="inlineStr">
         <is>
           <t>Japan Research</t>
         </is>
       </c>
-      <c r="M22" s="48" t="n"/>
-      <c r="N22" s="42" t="n"/>
-      <c r="O22" s="42" t="inlineStr">
+      <c r="O22" s="48" t="n"/>
+      <c r="P22" s="42" t="n"/>
+      <c r="Q22" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P22" s="42" t="n"/>
-      <c r="Q22" s="49" t="n"/>
+      <c r="R22" s="42" t="n"/>
+      <c r="S22" s="49" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="31">
       <c r="B23" s="42" t="inlineStr">
@@ -2703,20 +2948,22 @@
       </c>
       <c r="J23" s="52" t="n"/>
       <c r="K23" s="46" t="n"/>
-      <c r="L23" s="54" t="inlineStr">
+      <c r="L23" s="42" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="54" t="inlineStr">
         <is>
           <t>Korea Research</t>
         </is>
       </c>
-      <c r="M23" s="48" t="n"/>
-      <c r="N23" s="42" t="n"/>
-      <c r="O23" s="42" t="inlineStr">
+      <c r="O23" s="48" t="n"/>
+      <c r="P23" s="42" t="n"/>
+      <c r="Q23" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P23" s="42" t="n"/>
-      <c r="Q23" s="49" t="n"/>
+      <c r="R23" s="42" t="n"/>
+      <c r="S23" s="49" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="31">
       <c r="B24" s="42" t="inlineStr">
@@ -2761,20 +3008,22 @@
       </c>
       <c r="J24" s="52" t="n"/>
       <c r="K24" s="46" t="n"/>
-      <c r="L24" s="54" t="inlineStr">
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="54" t="inlineStr">
         <is>
           <t>Korea Research</t>
         </is>
       </c>
-      <c r="M24" s="48" t="n"/>
-      <c r="N24" s="42" t="n"/>
-      <c r="O24" s="42" t="inlineStr">
+      <c r="O24" s="48" t="n"/>
+      <c r="P24" s="42" t="n"/>
+      <c r="Q24" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P24" s="42" t="n"/>
-      <c r="Q24" s="49" t="n"/>
+      <c r="R24" s="42" t="n"/>
+      <c r="S24" s="49" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="31">
       <c r="B25" s="42" t="inlineStr">
@@ -2819,20 +3068,22 @@
       </c>
       <c r="J25" s="52" t="n"/>
       <c r="K25" s="46" t="n"/>
-      <c r="L25" s="54" t="inlineStr">
+      <c r="L25" s="42" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="54" t="inlineStr">
         <is>
           <t>Korea Research</t>
         </is>
       </c>
-      <c r="M25" s="48" t="n"/>
-      <c r="N25" s="42" t="n"/>
-      <c r="O25" s="42" t="inlineStr">
+      <c r="O25" s="48" t="n"/>
+      <c r="P25" s="42" t="n"/>
+      <c r="Q25" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P25" s="42" t="n"/>
-      <c r="Q25" s="49" t="n"/>
+      <c r="R25" s="42" t="n"/>
+      <c r="S25" s="49" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="31">
       <c r="B26" s="42" t="inlineStr">
@@ -2877,20 +3128,22 @@
       </c>
       <c r="J26" s="52" t="n"/>
       <c r="K26" s="46" t="n"/>
-      <c r="L26" s="54" t="inlineStr">
+      <c r="L26" s="42" t="n"/>
+      <c r="M26" s="42" t="n"/>
+      <c r="N26" s="54" t="inlineStr">
         <is>
           <t>Korea Research</t>
         </is>
       </c>
-      <c r="M26" s="48" t="n"/>
-      <c r="N26" s="42" t="n"/>
-      <c r="O26" s="42" t="inlineStr">
+      <c r="O26" s="48" t="n"/>
+      <c r="P26" s="42" t="n"/>
+      <c r="Q26" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P26" s="42" t="n"/>
-      <c r="Q26" s="49" t="n"/>
+      <c r="R26" s="42" t="n"/>
+      <c r="S26" s="49" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="31">
       <c r="B27" s="42" t="inlineStr">
@@ -2935,20 +3188,22 @@
       </c>
       <c r="J27" s="52" t="n"/>
       <c r="K27" s="46" t="n"/>
-      <c r="L27" s="54" t="inlineStr">
+      <c r="L27" s="42" t="n"/>
+      <c r="M27" s="42" t="n"/>
+      <c r="N27" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M27" s="48" t="n"/>
-      <c r="N27" s="42" t="n"/>
-      <c r="O27" s="42" t="inlineStr">
+      <c r="O27" s="48" t="n"/>
+      <c r="P27" s="42" t="n"/>
+      <c r="Q27" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P27" s="42" t="n"/>
-      <c r="Q27" s="49" t="n"/>
+      <c r="R27" s="42" t="n"/>
+      <c r="S27" s="49" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="31">
       <c r="B28" s="42" t="inlineStr">
@@ -2993,20 +3248,22 @@
       </c>
       <c r="J28" s="52" t="n"/>
       <c r="K28" s="46" t="n"/>
-      <c r="L28" s="54" t="inlineStr">
+      <c r="L28" s="42" t="n"/>
+      <c r="M28" s="42" t="n"/>
+      <c r="N28" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M28" s="48" t="n"/>
-      <c r="N28" s="42" t="n"/>
-      <c r="O28" s="42" t="inlineStr">
+      <c r="O28" s="48" t="n"/>
+      <c r="P28" s="42" t="n"/>
+      <c r="Q28" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P28" s="42" t="n"/>
-      <c r="Q28" s="49" t="n"/>
+      <c r="R28" s="42" t="n"/>
+      <c r="S28" s="49" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="31">
       <c r="B29" s="42" t="inlineStr">
@@ -3051,20 +3308,22 @@
       </c>
       <c r="J29" s="52" t="n"/>
       <c r="K29" s="46" t="n"/>
-      <c r="L29" s="54" t="inlineStr">
+      <c r="L29" s="42" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M29" s="48" t="n"/>
-      <c r="N29" s="42" t="n"/>
-      <c r="O29" s="42" t="inlineStr">
+      <c r="O29" s="48" t="n"/>
+      <c r="P29" s="42" t="n"/>
+      <c r="Q29" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P29" s="42" t="n"/>
-      <c r="Q29" s="49" t="n"/>
+      <c r="R29" s="42" t="n"/>
+      <c r="S29" s="49" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="31">
       <c r="B30" s="42" t="inlineStr">
@@ -3109,20 +3368,22 @@
       </c>
       <c r="J30" s="52" t="n"/>
       <c r="K30" s="46" t="n"/>
-      <c r="L30" s="54" t="inlineStr">
+      <c r="L30" s="42" t="n"/>
+      <c r="M30" s="42" t="n"/>
+      <c r="N30" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M30" s="48" t="n"/>
-      <c r="N30" s="42" t="n"/>
-      <c r="O30" s="42" t="inlineStr">
+      <c r="O30" s="48" t="n"/>
+      <c r="P30" s="42" t="n"/>
+      <c r="Q30" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P30" s="42" t="n"/>
-      <c r="Q30" s="49" t="n"/>
+      <c r="R30" s="42" t="n"/>
+      <c r="S30" s="49" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="31">
       <c r="B31" s="42" t="inlineStr">
@@ -3167,20 +3428,22 @@
       </c>
       <c r="J31" s="52" t="n"/>
       <c r="K31" s="46" t="n"/>
-      <c r="L31" s="54" t="inlineStr">
+      <c r="L31" s="42" t="n"/>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M31" s="48" t="n"/>
-      <c r="N31" s="42" t="n"/>
-      <c r="O31" s="42" t="inlineStr">
+      <c r="O31" s="48" t="n"/>
+      <c r="P31" s="42" t="n"/>
+      <c r="Q31" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P31" s="42" t="n"/>
-      <c r="Q31" s="49" t="n"/>
+      <c r="R31" s="42" t="n"/>
+      <c r="S31" s="49" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="31">
       <c r="B32" s="42" t="inlineStr">
@@ -3225,20 +3488,22 @@
       </c>
       <c r="J32" s="52" t="n"/>
       <c r="K32" s="46" t="n"/>
-      <c r="L32" s="54" t="inlineStr">
+      <c r="L32" s="42" t="n"/>
+      <c r="M32" s="42" t="n"/>
+      <c r="N32" s="54" t="inlineStr">
         <is>
           <t>Singapore Research</t>
         </is>
       </c>
-      <c r="M32" s="48" t="n"/>
-      <c r="N32" s="42" t="n"/>
-      <c r="O32" s="42" t="inlineStr">
+      <c r="O32" s="48" t="n"/>
+      <c r="P32" s="42" t="n"/>
+      <c r="Q32" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P32" s="42" t="n"/>
-      <c r="Q32" s="49" t="n"/>
+      <c r="R32" s="42" t="n"/>
+      <c r="S32" s="49" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="31">
       <c r="B33" s="42" t="inlineStr">
@@ -3283,19 +3548,21 @@
       </c>
       <c r="J33" s="52" t="n"/>
       <c r="K33" s="46" t="n"/>
-      <c r="L33" s="54" t="inlineStr">
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="42" t="n"/>
+      <c r="N33" s="54" t="inlineStr">
         <is>
           <t>Taiwan Research</t>
         </is>
       </c>
-      <c r="M33" s="48" t="n"/>
-      <c r="N33" s="42" t="n"/>
-      <c r="O33" s="42" t="inlineStr">
+      <c r="O33" s="48" t="n"/>
+      <c r="P33" s="42" t="n"/>
+      <c r="Q33" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P33" s="42" t="n"/>
+      <c r="R33" s="42" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="31">
       <c r="B34" s="42" t="inlineStr">
@@ -3340,19 +3607,21 @@
       </c>
       <c r="J34" s="52" t="n"/>
       <c r="K34" s="46" t="n"/>
-      <c r="L34" s="54" t="inlineStr">
+      <c r="L34" s="42" t="n"/>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="54" t="inlineStr">
         <is>
           <t>Taiwan Research</t>
         </is>
       </c>
-      <c r="M34" s="48" t="n"/>
-      <c r="N34" s="42" t="n"/>
-      <c r="O34" s="42" t="inlineStr">
+      <c r="O34" s="48" t="n"/>
+      <c r="P34" s="42" t="n"/>
+      <c r="Q34" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P34" s="42" t="n"/>
+      <c r="R34" s="42" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="31">
       <c r="B35" s="54" t="inlineStr">
@@ -3397,20 +3666,22 @@
       </c>
       <c r="J35" s="52" t="n"/>
       <c r="K35" s="46" t="n"/>
-      <c r="L35" s="54" t="inlineStr">
+      <c r="L35" s="42" t="n"/>
+      <c r="M35" s="42" t="n"/>
+      <c r="N35" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M35" s="48" t="n"/>
-      <c r="N35" s="42" t="n"/>
-      <c r="O35" s="42" t="inlineStr">
+      <c r="O35" s="48" t="n"/>
+      <c r="P35" s="42" t="n"/>
+      <c r="Q35" s="42" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="P35" s="42" t="n"/>
-      <c r="Q35" s="49" t="n"/>
+      <c r="R35" s="42" t="n"/>
+      <c r="S35" s="49" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="31">
       <c r="B36" s="54" t="inlineStr">
@@ -3455,24 +3726,26 @@
         </is>
       </c>
       <c r="K36" s="46" t="n"/>
-      <c r="L36" s="54" t="inlineStr">
+      <c r="L36" s="42" t="n"/>
+      <c r="M36" s="42" t="n"/>
+      <c r="N36" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M36" s="48" t="n"/>
-      <c r="N36" s="54" t="inlineStr">
+      <c r="O36" s="48" t="n"/>
+      <c r="P36" s="54" t="inlineStr">
         <is>
           <t>Done but on hold at the moment</t>
         </is>
       </c>
-      <c r="O36" s="42" t="inlineStr">
+      <c r="Q36" s="42" t="inlineStr">
         <is>
           <t>In-Country</t>
         </is>
       </c>
-      <c r="P36" s="42" t="n"/>
-      <c r="Q36" s="49" t="n"/>
+      <c r="R36" s="42" t="n"/>
+      <c r="S36" s="49" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="31">
       <c r="B37" s="54" t="inlineStr">
@@ -3515,20 +3788,22 @@
         <v>46195</v>
       </c>
       <c r="K37" s="46" t="n"/>
-      <c r="L37" s="54" t="inlineStr">
+      <c r="L37" s="42" t="n"/>
+      <c r="M37" s="42" t="n"/>
+      <c r="N37" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M37" s="48" t="n"/>
-      <c r="N37" s="42" t="n"/>
-      <c r="O37" s="42" t="inlineStr">
+      <c r="O37" s="48" t="n"/>
+      <c r="P37" s="42" t="n"/>
+      <c r="Q37" s="42" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="P37" s="42" t="n"/>
-      <c r="Q37" s="49" t="n"/>
+      <c r="R37" s="42" t="n"/>
+      <c r="S37" s="49" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="31">
       <c r="B38" s="54" t="inlineStr">
@@ -3571,20 +3846,22 @@
         <v>46255</v>
       </c>
       <c r="K38" s="46" t="n"/>
-      <c r="L38" s="54" t="inlineStr">
+      <c r="L38" s="42" t="n"/>
+      <c r="M38" s="42" t="n"/>
+      <c r="N38" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M38" s="48" t="n"/>
-      <c r="N38" s="42" t="n"/>
-      <c r="O38" s="42" t="inlineStr">
+      <c r="O38" s="48" t="n"/>
+      <c r="P38" s="42" t="n"/>
+      <c r="Q38" s="42" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="P38" s="42" t="n"/>
-      <c r="Q38" s="49" t="n"/>
+      <c r="R38" s="42" t="n"/>
+      <c r="S38" s="49" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="31">
       <c r="B39" s="54" t="inlineStr">
@@ -3629,20 +3906,22 @@
       </c>
       <c r="J39" s="52" t="n"/>
       <c r="K39" s="46" t="n"/>
-      <c r="L39" s="54" t="inlineStr">
+      <c r="L39" s="42" t="n"/>
+      <c r="M39" s="42" t="n"/>
+      <c r="N39" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M39" s="48" t="n"/>
-      <c r="N39" s="42" t="n"/>
-      <c r="O39" s="42" t="inlineStr">
+      <c r="O39" s="48" t="n"/>
+      <c r="P39" s="42" t="n"/>
+      <c r="Q39" s="42" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="P39" s="42" t="n"/>
-      <c r="Q39" s="49" t="n"/>
+      <c r="R39" s="42" t="n"/>
+      <c r="S39" s="49" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="31">
       <c r="B40" s="54" t="inlineStr">
@@ -3687,20 +3966,22 @@
       </c>
       <c r="J40" s="52" t="n"/>
       <c r="K40" s="46" t="n"/>
-      <c r="L40" s="54" t="inlineStr">
+      <c r="L40" s="42" t="n"/>
+      <c r="M40" s="42" t="n"/>
+      <c r="N40" s="54" t="inlineStr">
         <is>
           <t>APAC Research</t>
         </is>
       </c>
-      <c r="M40" s="48" t="n"/>
-      <c r="N40" s="42" t="n"/>
-      <c r="O40" s="42" t="inlineStr">
+      <c r="O40" s="48" t="n"/>
+      <c r="P40" s="42" t="n"/>
+      <c r="Q40" s="42" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="P40" s="42" t="n"/>
-      <c r="Q40" s="49" t="n"/>
+      <c r="R40" s="42" t="n"/>
+      <c r="S40" s="49" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="31">
       <c r="B41" s="42" t="n"/>
@@ -3714,11 +3995,13 @@
       <c r="J41" s="43" t="n"/>
       <c r="K41" s="46" t="n"/>
       <c r="L41" s="42" t="n"/>
-      <c r="M41" s="48" t="n"/>
+      <c r="M41" s="42" t="n"/>
       <c r="N41" s="42" t="n"/>
-      <c r="O41" s="42" t="n"/>
+      <c r="O41" s="48" t="n"/>
       <c r="P41" s="42" t="n"/>
-      <c r="Q41" s="49" t="n"/>
+      <c r="Q41" s="42" t="n"/>
+      <c r="R41" s="42" t="n"/>
+      <c r="S41" s="49" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="31">
       <c r="B42" s="42" t="n"/>
@@ -3732,11 +4015,13 @@
       <c r="J42" s="43" t="n"/>
       <c r="K42" s="46" t="n"/>
       <c r="L42" s="42" t="n"/>
-      <c r="M42" s="48" t="n"/>
+      <c r="M42" s="42" t="n"/>
       <c r="N42" s="42" t="n"/>
-      <c r="O42" s="42" t="n"/>
+      <c r="O42" s="48" t="n"/>
       <c r="P42" s="42" t="n"/>
-      <c r="Q42" s="49" t="n"/>
+      <c r="Q42" s="42" t="n"/>
+      <c r="R42" s="42" t="n"/>
+      <c r="S42" s="49" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="31">
       <c r="B43" s="42" t="n"/>
@@ -3750,11 +4035,13 @@
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="46" t="n"/>
       <c r="L43" s="42" t="n"/>
-      <c r="M43" s="48" t="n"/>
+      <c r="M43" s="42" t="n"/>
       <c r="N43" s="42" t="n"/>
-      <c r="O43" s="42" t="n"/>
+      <c r="O43" s="48" t="n"/>
       <c r="P43" s="42" t="n"/>
-      <c r="Q43" s="49" t="n"/>
+      <c r="Q43" s="42" t="n"/>
+      <c r="R43" s="42" t="n"/>
+      <c r="S43" s="49" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="31">
       <c r="B44" s="42" t="n"/>
@@ -3768,11 +4055,13 @@
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="46" t="n"/>
       <c r="L44" s="42" t="n"/>
-      <c r="M44" s="48" t="n"/>
+      <c r="M44" s="42" t="n"/>
       <c r="N44" s="42" t="n"/>
-      <c r="O44" s="42" t="n"/>
+      <c r="O44" s="48" t="n"/>
       <c r="P44" s="42" t="n"/>
-      <c r="Q44" s="49" t="n"/>
+      <c r="Q44" s="42" t="n"/>
+      <c r="R44" s="42" t="n"/>
+      <c r="S44" s="49" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="31">
       <c r="B45" s="42" t="n"/>
@@ -3786,11 +4075,13 @@
       <c r="J45" s="43" t="n"/>
       <c r="K45" s="46" t="n"/>
       <c r="L45" s="42" t="n"/>
-      <c r="M45" s="48" t="n"/>
+      <c r="M45" s="42" t="n"/>
       <c r="N45" s="42" t="n"/>
-      <c r="O45" s="42" t="n"/>
+      <c r="O45" s="48" t="n"/>
       <c r="P45" s="42" t="n"/>
-      <c r="Q45" s="49" t="n"/>
+      <c r="Q45" s="42" t="n"/>
+      <c r="R45" s="42" t="n"/>
+      <c r="S45" s="49" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="31">
       <c r="B46" s="42" t="n"/>
@@ -3804,11 +4095,13 @@
       <c r="J46" s="43" t="n"/>
       <c r="K46" s="46" t="n"/>
       <c r="L46" s="42" t="n"/>
-      <c r="M46" s="48" t="n"/>
+      <c r="M46" s="42" t="n"/>
       <c r="N46" s="42" t="n"/>
-      <c r="O46" s="42" t="n"/>
+      <c r="O46" s="48" t="n"/>
       <c r="P46" s="42" t="n"/>
-      <c r="Q46" s="49" t="n"/>
+      <c r="Q46" s="42" t="n"/>
+      <c r="R46" s="42" t="n"/>
+      <c r="S46" s="49" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="31">
       <c r="B47" s="42" t="n"/>
@@ -3822,11 +4115,13 @@
       <c r="J47" s="43" t="n"/>
       <c r="K47" s="46" t="n"/>
       <c r="L47" s="42" t="n"/>
-      <c r="M47" s="48" t="n"/>
+      <c r="M47" s="42" t="n"/>
       <c r="N47" s="42" t="n"/>
-      <c r="O47" s="42" t="n"/>
+      <c r="O47" s="48" t="n"/>
       <c r="P47" s="42" t="n"/>
-      <c r="Q47" s="49" t="n"/>
+      <c r="Q47" s="42" t="n"/>
+      <c r="R47" s="42" t="n"/>
+      <c r="S47" s="49" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="31">
       <c r="B48" s="42" t="n"/>
@@ -3840,11 +4135,13 @@
       <c r="J48" s="43" t="n"/>
       <c r="K48" s="46" t="n"/>
       <c r="L48" s="42" t="n"/>
-      <c r="M48" s="48" t="n"/>
+      <c r="M48" s="42" t="n"/>
       <c r="N48" s="42" t="n"/>
-      <c r="O48" s="42" t="n"/>
+      <c r="O48" s="48" t="n"/>
       <c r="P48" s="42" t="n"/>
-      <c r="Q48" s="49" t="n"/>
+      <c r="Q48" s="42" t="n"/>
+      <c r="R48" s="42" t="n"/>
+      <c r="S48" s="49" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="31">
       <c r="B49" s="42" t="n"/>
@@ -3858,11 +4155,13 @@
       <c r="J49" s="43" t="n"/>
       <c r="K49" s="46" t="n"/>
       <c r="L49" s="42" t="n"/>
-      <c r="M49" s="48" t="n"/>
+      <c r="M49" s="42" t="n"/>
       <c r="N49" s="42" t="n"/>
-      <c r="O49" s="42" t="n"/>
+      <c r="O49" s="48" t="n"/>
       <c r="P49" s="42" t="n"/>
-      <c r="Q49" s="49" t="n"/>
+      <c r="Q49" s="42" t="n"/>
+      <c r="R49" s="42" t="n"/>
+      <c r="S49" s="49" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="31">
       <c r="B50" s="42" t="n"/>
@@ -3876,11 +4175,13 @@
       <c r="J50" s="43" t="n"/>
       <c r="K50" s="46" t="n"/>
       <c r="L50" s="42" t="n"/>
-      <c r="M50" s="48" t="n"/>
+      <c r="M50" s="42" t="n"/>
       <c r="N50" s="42" t="n"/>
-      <c r="O50" s="42" t="n"/>
+      <c r="O50" s="48" t="n"/>
       <c r="P50" s="42" t="n"/>
-      <c r="Q50" s="49" t="n"/>
+      <c r="Q50" s="42" t="n"/>
+      <c r="R50" s="42" t="n"/>
+      <c r="S50" s="49" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="31">
       <c r="B51" s="42" t="n"/>
@@ -3894,11 +4195,13 @@
       <c r="J51" s="43" t="n"/>
       <c r="K51" s="46" t="n"/>
       <c r="L51" s="42" t="n"/>
-      <c r="M51" s="48" t="n"/>
+      <c r="M51" s="42" t="n"/>
       <c r="N51" s="42" t="n"/>
-      <c r="O51" s="42" t="n"/>
+      <c r="O51" s="48" t="n"/>
       <c r="P51" s="42" t="n"/>
-      <c r="Q51" s="49" t="n"/>
+      <c r="Q51" s="42" t="n"/>
+      <c r="R51" s="42" t="n"/>
+      <c r="S51" s="49" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="31">
       <c r="B52" s="42" t="n"/>
@@ -3912,11 +4215,13 @@
       <c r="J52" s="43" t="n"/>
       <c r="K52" s="46" t="n"/>
       <c r="L52" s="42" t="n"/>
-      <c r="M52" s="48" t="n"/>
+      <c r="M52" s="42" t="n"/>
       <c r="N52" s="42" t="n"/>
-      <c r="O52" s="42" t="n"/>
+      <c r="O52" s="48" t="n"/>
       <c r="P52" s="42" t="n"/>
-      <c r="Q52" s="49" t="n"/>
+      <c r="Q52" s="42" t="n"/>
+      <c r="R52" s="42" t="n"/>
+      <c r="S52" s="49" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="31">
       <c r="B53" s="42" t="n"/>
@@ -3930,11 +4235,13 @@
       <c r="J53" s="43" t="n"/>
       <c r="K53" s="46" t="n"/>
       <c r="L53" s="42" t="n"/>
-      <c r="M53" s="48" t="n"/>
+      <c r="M53" s="42" t="n"/>
       <c r="N53" s="42" t="n"/>
-      <c r="O53" s="42" t="n"/>
+      <c r="O53" s="48" t="n"/>
       <c r="P53" s="42" t="n"/>
-      <c r="Q53" s="49" t="n"/>
+      <c r="Q53" s="42" t="n"/>
+      <c r="R53" s="42" t="n"/>
+      <c r="S53" s="49" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="31">
       <c r="B54" s="42" t="n"/>
@@ -3948,11 +4255,13 @@
       <c r="J54" s="43" t="n"/>
       <c r="K54" s="46" t="n"/>
       <c r="L54" s="42" t="n"/>
-      <c r="M54" s="48" t="n"/>
+      <c r="M54" s="42" t="n"/>
       <c r="N54" s="42" t="n"/>
-      <c r="O54" s="42" t="n"/>
+      <c r="O54" s="48" t="n"/>
       <c r="P54" s="42" t="n"/>
-      <c r="Q54" s="49" t="n"/>
+      <c r="Q54" s="42" t="n"/>
+      <c r="R54" s="42" t="n"/>
+      <c r="S54" s="49" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="31">
       <c r="B55" s="42" t="n"/>
@@ -3966,11 +4275,13 @@
       <c r="J55" s="43" t="n"/>
       <c r="K55" s="46" t="n"/>
       <c r="L55" s="42" t="n"/>
-      <c r="M55" s="48" t="n"/>
+      <c r="M55" s="42" t="n"/>
       <c r="N55" s="42" t="n"/>
-      <c r="O55" s="42" t="n"/>
+      <c r="O55" s="48" t="n"/>
       <c r="P55" s="42" t="n"/>
-      <c r="Q55" s="49" t="n"/>
+      <c r="Q55" s="42" t="n"/>
+      <c r="R55" s="42" t="n"/>
+      <c r="S55" s="49" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="31">
       <c r="B56" s="42" t="n"/>
@@ -3984,11 +4295,13 @@
       <c r="J56" s="43" t="n"/>
       <c r="K56" s="46" t="n"/>
       <c r="L56" s="42" t="n"/>
-      <c r="M56" s="48" t="n"/>
+      <c r="M56" s="42" t="n"/>
       <c r="N56" s="42" t="n"/>
-      <c r="O56" s="42" t="n"/>
+      <c r="O56" s="48" t="n"/>
       <c r="P56" s="42" t="n"/>
-      <c r="Q56" s="49" t="n"/>
+      <c r="Q56" s="42" t="n"/>
+      <c r="R56" s="42" t="n"/>
+      <c r="S56" s="49" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="31">
       <c r="B57" s="42" t="n"/>
@@ -4002,11 +4315,13 @@
       <c r="J57" s="43" t="n"/>
       <c r="K57" s="46" t="n"/>
       <c r="L57" s="42" t="n"/>
-      <c r="M57" s="48" t="n"/>
+      <c r="M57" s="42" t="n"/>
       <c r="N57" s="42" t="n"/>
-      <c r="O57" s="42" t="n"/>
+      <c r="O57" s="48" t="n"/>
       <c r="P57" s="42" t="n"/>
-      <c r="Q57" s="49" t="n"/>
+      <c r="Q57" s="42" t="n"/>
+      <c r="R57" s="42" t="n"/>
+      <c r="S57" s="49" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="31">
       <c r="B58" s="42" t="n"/>
@@ -4020,11 +4335,13 @@
       <c r="J58" s="43" t="n"/>
       <c r="K58" s="46" t="n"/>
       <c r="L58" s="42" t="n"/>
-      <c r="M58" s="48" t="n"/>
+      <c r="M58" s="42" t="n"/>
       <c r="N58" s="42" t="n"/>
-      <c r="O58" s="42" t="n"/>
+      <c r="O58" s="48" t="n"/>
       <c r="P58" s="42" t="n"/>
-      <c r="Q58" s="49" t="n"/>
+      <c r="Q58" s="42" t="n"/>
+      <c r="R58" s="42" t="n"/>
+      <c r="S58" s="49" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="31">
       <c r="B59" s="42" t="n"/>
@@ -4038,11 +4355,13 @@
       <c r="J59" s="43" t="n"/>
       <c r="K59" s="46" t="n"/>
       <c r="L59" s="42" t="n"/>
-      <c r="M59" s="48" t="n"/>
+      <c r="M59" s="42" t="n"/>
       <c r="N59" s="42" t="n"/>
-      <c r="O59" s="42" t="n"/>
+      <c r="O59" s="48" t="n"/>
       <c r="P59" s="42" t="n"/>
-      <c r="Q59" s="49" t="n"/>
+      <c r="Q59" s="42" t="n"/>
+      <c r="R59" s="42" t="n"/>
+      <c r="S59" s="49" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="31">
       <c r="B60" s="42" t="n"/>
@@ -4056,11 +4375,13 @@
       <c r="J60" s="43" t="n"/>
       <c r="K60" s="46" t="n"/>
       <c r="L60" s="42" t="n"/>
-      <c r="M60" s="48" t="n"/>
+      <c r="M60" s="42" t="n"/>
       <c r="N60" s="42" t="n"/>
-      <c r="O60" s="42" t="n"/>
+      <c r="O60" s="48" t="n"/>
       <c r="P60" s="42" t="n"/>
-      <c r="Q60" s="49" t="n"/>
+      <c r="Q60" s="42" t="n"/>
+      <c r="R60" s="42" t="n"/>
+      <c r="S60" s="49" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="31">
       <c r="B61" s="42" t="n"/>
@@ -4074,11 +4395,13 @@
       <c r="J61" s="43" t="n"/>
       <c r="K61" s="46" t="n"/>
       <c r="L61" s="42" t="n"/>
-      <c r="M61" s="48" t="n"/>
+      <c r="M61" s="42" t="n"/>
       <c r="N61" s="42" t="n"/>
-      <c r="O61" s="42" t="n"/>
+      <c r="O61" s="48" t="n"/>
       <c r="P61" s="42" t="n"/>
-      <c r="Q61" s="49" t="n"/>
+      <c r="Q61" s="42" t="n"/>
+      <c r="R61" s="42" t="n"/>
+      <c r="S61" s="49" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="31">
       <c r="B62" s="42" t="n"/>
@@ -4092,11 +4415,13 @@
       <c r="J62" s="43" t="n"/>
       <c r="K62" s="46" t="n"/>
       <c r="L62" s="42" t="n"/>
-      <c r="M62" s="48" t="n"/>
+      <c r="M62" s="42" t="n"/>
       <c r="N62" s="42" t="n"/>
-      <c r="O62" s="42" t="n"/>
+      <c r="O62" s="48" t="n"/>
       <c r="P62" s="42" t="n"/>
-      <c r="Q62" s="49" t="n"/>
+      <c r="Q62" s="42" t="n"/>
+      <c r="R62" s="42" t="n"/>
+      <c r="S62" s="49" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="31">
       <c r="B63" s="42" t="n"/>
@@ -4110,11 +4435,13 @@
       <c r="J63" s="43" t="n"/>
       <c r="K63" s="46" t="n"/>
       <c r="L63" s="42" t="n"/>
-      <c r="M63" s="48" t="n"/>
+      <c r="M63" s="42" t="n"/>
       <c r="N63" s="42" t="n"/>
-      <c r="O63" s="42" t="n"/>
+      <c r="O63" s="48" t="n"/>
       <c r="P63" s="42" t="n"/>
-      <c r="Q63" s="49" t="n"/>
+      <c r="Q63" s="42" t="n"/>
+      <c r="R63" s="42" t="n"/>
+      <c r="S63" s="49" t="n"/>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="31">
       <c r="B64" s="42" t="n"/>
@@ -4128,11 +4455,13 @@
       <c r="J64" s="43" t="n"/>
       <c r="K64" s="46" t="n"/>
       <c r="L64" s="42" t="n"/>
-      <c r="M64" s="48" t="n"/>
+      <c r="M64" s="42" t="n"/>
       <c r="N64" s="42" t="n"/>
-      <c r="O64" s="42" t="n"/>
+      <c r="O64" s="48" t="n"/>
       <c r="P64" s="42" t="n"/>
-      <c r="Q64" s="49" t="n"/>
+      <c r="Q64" s="42" t="n"/>
+      <c r="R64" s="42" t="n"/>
+      <c r="S64" s="49" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="31">
       <c r="B65" s="42" t="n"/>
@@ -4146,11 +4475,13 @@
       <c r="J65" s="43" t="n"/>
       <c r="K65" s="46" t="n"/>
       <c r="L65" s="42" t="n"/>
-      <c r="M65" s="48" t="n"/>
+      <c r="M65" s="42" t="n"/>
       <c r="N65" s="42" t="n"/>
-      <c r="O65" s="42" t="n"/>
+      <c r="O65" s="48" t="n"/>
       <c r="P65" s="42" t="n"/>
-      <c r="Q65" s="49" t="n"/>
+      <c r="Q65" s="42" t="n"/>
+      <c r="R65" s="42" t="n"/>
+      <c r="S65" s="49" t="n"/>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="31">
       <c r="B66" s="42" t="n"/>
@@ -4164,9 +4495,11 @@
       <c r="J66" s="43" t="n"/>
       <c r="K66" s="46" t="n"/>
       <c r="L66" s="42" t="n"/>
-      <c r="M66" s="48" t="n"/>
+      <c r="M66" s="42" t="n"/>
       <c r="N66" s="42" t="n"/>
-      <c r="O66" s="42" t="n"/>
+      <c r="O66" s="48" t="n"/>
+      <c r="P66" s="42" t="n"/>
+      <c r="Q66" s="42" t="n"/>
     </row>
     <row r="67" ht="14.25" customHeight="1" s="31">
       <c r="B67" s="42" t="n"/>
@@ -4180,9 +4513,11 @@
       <c r="J67" s="43" t="n"/>
       <c r="K67" s="46" t="n"/>
       <c r="L67" s="42" t="n"/>
-      <c r="M67" s="48" t="n"/>
+      <c r="M67" s="42" t="n"/>
       <c r="N67" s="42" t="n"/>
-      <c r="O67" s="42" t="n"/>
+      <c r="O67" s="48" t="n"/>
+      <c r="P67" s="42" t="n"/>
+      <c r="Q67" s="42" t="n"/>
     </row>
     <row r="68" ht="14.25" customHeight="1" s="31">
       <c r="B68" s="42" t="n"/>
@@ -4196,9 +4531,11 @@
       <c r="J68" s="43" t="n"/>
       <c r="K68" s="46" t="n"/>
       <c r="L68" s="42" t="n"/>
-      <c r="M68" s="48" t="n"/>
+      <c r="M68" s="42" t="n"/>
       <c r="N68" s="42" t="n"/>
-      <c r="O68" s="42" t="n"/>
+      <c r="O68" s="48" t="n"/>
+      <c r="P68" s="42" t="n"/>
+      <c r="Q68" s="42" t="n"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" s="31">
       <c r="B69" s="42" t="n"/>
@@ -4212,9 +4549,11 @@
       <c r="J69" s="43" t="n"/>
       <c r="K69" s="46" t="n"/>
       <c r="L69" s="42" t="n"/>
-      <c r="M69" s="48" t="n"/>
+      <c r="M69" s="42" t="n"/>
       <c r="N69" s="42" t="n"/>
-      <c r="O69" s="42" t="n"/>
+      <c r="O69" s="48" t="n"/>
+      <c r="P69" s="42" t="n"/>
+      <c r="Q69" s="42" t="n"/>
     </row>
     <row r="70" ht="14.25" customHeight="1" s="31">
       <c r="B70" s="42" t="n"/>
@@ -4228,9 +4567,11 @@
       <c r="J70" s="43" t="n"/>
       <c r="K70" s="46" t="n"/>
       <c r="L70" s="42" t="n"/>
-      <c r="M70" s="48" t="n"/>
+      <c r="M70" s="42" t="n"/>
       <c r="N70" s="42" t="n"/>
-      <c r="O70" s="42" t="n"/>
+      <c r="O70" s="48" t="n"/>
+      <c r="P70" s="42" t="n"/>
+      <c r="Q70" s="42" t="n"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="31">
       <c r="B71" s="42" t="n"/>
@@ -4244,9 +4585,11 @@
       <c r="J71" s="43" t="n"/>
       <c r="K71" s="46" t="n"/>
       <c r="L71" s="42" t="n"/>
-      <c r="M71" s="48" t="n"/>
+      <c r="M71" s="42" t="n"/>
       <c r="N71" s="42" t="n"/>
-      <c r="O71" s="42" t="n"/>
+      <c r="O71" s="48" t="n"/>
+      <c r="P71" s="42" t="n"/>
+      <c r="Q71" s="42" t="n"/>
     </row>
     <row r="72" ht="14.25" customHeight="1" s="31">
       <c r="B72" s="42" t="n"/>
@@ -4260,9 +4603,11 @@
       <c r="J72" s="43" t="n"/>
       <c r="K72" s="46" t="n"/>
       <c r="L72" s="42" t="n"/>
-      <c r="M72" s="48" t="n"/>
+      <c r="M72" s="42" t="n"/>
       <c r="N72" s="42" t="n"/>
-      <c r="O72" s="42" t="n"/>
+      <c r="O72" s="48" t="n"/>
+      <c r="P72" s="42" t="n"/>
+      <c r="Q72" s="42" t="n"/>
     </row>
     <row r="73" ht="14.25" customHeight="1" s="31">
       <c r="B73" s="42" t="n"/>
@@ -4276,9 +4621,11 @@
       <c r="J73" s="43" t="n"/>
       <c r="K73" s="46" t="n"/>
       <c r="L73" s="42" t="n"/>
-      <c r="M73" s="48" t="n"/>
+      <c r="M73" s="42" t="n"/>
       <c r="N73" s="42" t="n"/>
-      <c r="O73" s="42" t="n"/>
+      <c r="O73" s="48" t="n"/>
+      <c r="P73" s="42" t="n"/>
+      <c r="Q73" s="42" t="n"/>
     </row>
     <row r="74" ht="14.25" customHeight="1" s="31">
       <c r="B74" s="42" t="n"/>
@@ -4292,9 +4639,11 @@
       <c r="J74" s="43" t="n"/>
       <c r="K74" s="46" t="n"/>
       <c r="L74" s="42" t="n"/>
-      <c r="M74" s="48" t="n"/>
+      <c r="M74" s="42" t="n"/>
       <c r="N74" s="42" t="n"/>
-      <c r="O74" s="42" t="n"/>
+      <c r="O74" s="48" t="n"/>
+      <c r="P74" s="42" t="n"/>
+      <c r="Q74" s="42" t="n"/>
     </row>
     <row r="75" ht="14.25" customHeight="1" s="31">
       <c r="B75" s="42" t="n"/>
@@ -4308,9 +4657,11 @@
       <c r="J75" s="43" t="n"/>
       <c r="K75" s="46" t="n"/>
       <c r="L75" s="42" t="n"/>
-      <c r="M75" s="48" t="n"/>
+      <c r="M75" s="42" t="n"/>
       <c r="N75" s="42" t="n"/>
-      <c r="O75" s="42" t="n"/>
+      <c r="O75" s="48" t="n"/>
+      <c r="P75" s="42" t="n"/>
+      <c r="Q75" s="42" t="n"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" s="31">
       <c r="B76" s="42" t="n"/>
@@ -4324,9 +4675,11 @@
       <c r="J76" s="43" t="n"/>
       <c r="K76" s="46" t="n"/>
       <c r="L76" s="42" t="n"/>
-      <c r="M76" s="48" t="n"/>
+      <c r="M76" s="42" t="n"/>
       <c r="N76" s="42" t="n"/>
-      <c r="O76" s="42" t="n"/>
+      <c r="O76" s="48" t="n"/>
+      <c r="P76" s="42" t="n"/>
+      <c r="Q76" s="42" t="n"/>
     </row>
     <row r="77" ht="14.25" customHeight="1" s="31">
       <c r="B77" s="42" t="n"/>
@@ -4340,9 +4693,11 @@
       <c r="J77" s="43" t="n"/>
       <c r="K77" s="46" t="n"/>
       <c r="L77" s="42" t="n"/>
-      <c r="M77" s="48" t="n"/>
+      <c r="M77" s="42" t="n"/>
       <c r="N77" s="42" t="n"/>
-      <c r="O77" s="42" t="n"/>
+      <c r="O77" s="48" t="n"/>
+      <c r="P77" s="42" t="n"/>
+      <c r="Q77" s="42" t="n"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" s="31">
       <c r="B78" s="42" t="n"/>
@@ -4356,9 +4711,11 @@
       <c r="J78" s="43" t="n"/>
       <c r="K78" s="46" t="n"/>
       <c r="L78" s="42" t="n"/>
-      <c r="M78" s="48" t="n"/>
+      <c r="M78" s="42" t="n"/>
       <c r="N78" s="42" t="n"/>
-      <c r="O78" s="42" t="n"/>
+      <c r="O78" s="48" t="n"/>
+      <c r="P78" s="42" t="n"/>
+      <c r="Q78" s="42" t="n"/>
     </row>
     <row r="79" ht="14.25" customHeight="1" s="31">
       <c r="B79" s="42" t="n"/>
@@ -4372,9 +4729,11 @@
       <c r="J79" s="43" t="n"/>
       <c r="K79" s="46" t="n"/>
       <c r="L79" s="42" t="n"/>
-      <c r="M79" s="48" t="n"/>
+      <c r="M79" s="42" t="n"/>
       <c r="N79" s="42" t="n"/>
-      <c r="O79" s="42" t="n"/>
+      <c r="O79" s="48" t="n"/>
+      <c r="P79" s="42" t="n"/>
+      <c r="Q79" s="42" t="n"/>
     </row>
     <row r="80" ht="14.25" customHeight="1" s="31">
       <c r="B80" s="42" t="n"/>
@@ -4388,9 +4747,11 @@
       <c r="J80" s="43" t="n"/>
       <c r="K80" s="46" t="n"/>
       <c r="L80" s="42" t="n"/>
-      <c r="M80" s="48" t="n"/>
+      <c r="M80" s="42" t="n"/>
       <c r="N80" s="42" t="n"/>
-      <c r="O80" s="42" t="n"/>
+      <c r="O80" s="48" t="n"/>
+      <c r="P80" s="42" t="n"/>
+      <c r="Q80" s="42" t="n"/>
     </row>
     <row r="81" ht="14.25" customHeight="1" s="31">
       <c r="B81" s="42" t="n"/>
@@ -4404,53 +4765,72 @@
       <c r="J81" s="43" t="n"/>
       <c r="K81" s="46" t="n"/>
       <c r="L81" s="42" t="n"/>
-      <c r="M81" s="48" t="n"/>
+      <c r="M81" s="42" t="n"/>
       <c r="N81" s="42" t="n"/>
-      <c r="O81" s="42" t="n"/>
+      <c r="O81" s="48" t="n"/>
+      <c r="P81" s="42" t="n"/>
+      <c r="Q81" s="42" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:P81"/>
-  <conditionalFormatting sqref="D3:D81">
-    <cfRule type="duplicateValues" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0"/>
+  <autoFilter ref="B2:R81"/>
+  <conditionalFormatting sqref="D3:D563">
+    <cfRule type="duplicateValues" priority="1" dxfId="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:P81">
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
+  <conditionalFormatting sqref="C3:R563">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="10">
       <formula>"TBD"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I81">
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
+  <conditionalFormatting sqref="I3:I563">
+    <cfRule type="expression" priority="3" dxfId="9">
       <formula>AND(OR($H3="Annually",$H3="Biannually",$H3="Quarterly"),TRIM($I3)="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation sqref="B3:B563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Country" prompt="Pick from the dropdown." type="list" errorStyle="stop" operator="between">
+  <conditionalFormatting sqref="K3:K563">
+    <cfRule type="expression" priority="4" dxfId="9">
+      <formula>AND(OR($H3="Annually",$H3="Biannually",$H3="Quarterly",$H3="Monthly"),TRIM($K3)="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M563">
+    <cfRule type="expression" priority="5" dxfId="9">
+      <formula>AND($M3="Confirmed",TRIM($J3)="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="9">
+      <formula>AND($M3="Estimated",TRIM($L3)="",NOT(OR($H3="Annually",$H3="Biannually",$H3="Quarterly",$H3="Monthly")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L563">
+    <cfRule type="expression" priority="7" dxfId="10">
+      <formula>AND(TRIM($L3)&lt;&gt;"",OR($H3="Ad Hoc",TRIM($H3)=""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="9">
+    <dataValidation sqref="B3:B563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Country" prompt="Pick from the dropdown." type="list">
       <formula1>'Reference Lists'!$B$4:$B$18</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F3:F563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Publication Type" prompt="Pick one from the dropdown." type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F3:F563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Publication Type" prompt="Pick one from the dropdown." type="list">
       <formula1>'Reference Lists'!$D$4:$D$10</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H3:H563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Frequency" prompt="Annually / Biannually / Quarterly / Monthly / Ad Hoc." type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H3:H563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Frequency" prompt="Annually / Biannually / Quarterly / Monthly / Ad Hoc." type="list">
       <formula1>'Reference Lists'!$H$4:$H$8</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J3:J563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Expected Publication Date" prompt="YYYY-MM-DD. Required for Ad Hoc; leave blank for recurring." type="date" errorStyle="stop" operator="between">
+    <dataValidation sqref="J3:J563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Expected Publication Date" prompt="YYYY-MM-DD. Confirmed date. For recurring rows it overrides the estimated timing for the NEXT occurrence only." type="date">
       <formula1>0</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K3:K563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Start Date" prompt="YYYY-MM-DD. For recurring rows: first instance to project FROM. Leave blank to start from upload date." type="date" errorStyle="stop" operator="between">
+    <dataValidation sqref="K3:K563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Start Date" prompt="YYYY-MM-DD. REQUIRED for recurring rows: the series start. Recurring instances are generated on/after this date. Blank = project from upload date." type="date">
       <formula1>0</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O3:O563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Report Scope" prompt="Regional or In-Country." type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L3:L563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Recurring Timing Window" prompt="Used when the exact date is not yet known. Early month=~5th, Mid-month=~15th, Late month=~25th (snapped to a business day). TBD/blank = last business day of month." type="list">
+      <formula1>'Reference Lists'!$J$4:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Date Confidence" prompt="Optional. Blank = platform infers (Confirmed if exact date, else Estimated if timing window, else TBD). A value entered here OVERRIDES inference." type="list">
+      <formula1>'Reference Lists'!$K$4:$K$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Report Scope" prompt="Regional or In-Country." type="list">
       <formula1>'Reference Lists'!$F$4:$F$5</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="P3:P563" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status (future)" prompt="Workflow stage." type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R3:R563" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Status (future)" prompt="Workflow stage." type="list">
       <formula1>'Reference Lists'!$G$4:$G$9</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -4465,8 +4845,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B1:I30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.25" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" style="30" min="1" max="1"/>
     <col width="18" customWidth="1" style="30" min="2" max="7"/>
@@ -4522,6 +4902,16 @@
           <t>Recurring Months</t>
         </is>
       </c>
+      <c r="J3" s="60" t="inlineStr">
+        <is>
+          <t>Recurring Timing Window</t>
+        </is>
+      </c>
+      <c r="K3" s="60" t="inlineStr">
+        <is>
+          <t>Date Confidence</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="31">
       <c r="B4" s="58" t="inlineStr">
@@ -4564,6 +4954,16 @@
           <t>Jan</t>
         </is>
       </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>Early month</t>
+        </is>
+      </c>
+      <c r="K4" s="30" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="31">
       <c r="B5" s="58" t="inlineStr">
@@ -4606,6 +5006,16 @@
           <t>Feb</t>
         </is>
       </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>Mid-month</t>
+        </is>
+      </c>
+      <c r="K5" s="30" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="31">
       <c r="B6" s="58" t="inlineStr">
@@ -4643,6 +5053,16 @@
           <t>Mar</t>
         </is>
       </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>Late month</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="31">
       <c r="B7" s="58" t="inlineStr">
@@ -4678,6 +5098,11 @@
       <c r="I7" s="58" t="inlineStr">
         <is>
           <t>Apr</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
